--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D241"/>
+  <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4243,20 +4243,14 @@
           <t>E1Xs9lu2</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B239" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D239" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="240">
@@ -4265,20 +4259,14 @@
           <t>ITdtTrn2</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B240" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C240" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D240" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="241">
@@ -4287,19 +4275,211 @@
           <t>IZqoAH3k</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B241" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C241" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D241" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>fcYpyo85</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>fqgCMogC</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>QwI4i6hn</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>jPRgZOxI</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
         <is>
           <t>2.90</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>3.40</t>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>OxQ1X27U</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.50</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D250"/>
+  <dimension ref="A1:D258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4291,20 +4291,14 @@
           <t>WhAFMMRi</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B242" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C242" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D242" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="243">
@@ -4313,20 +4307,14 @@
           <t>vJDNK0d4</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B243" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="244">
@@ -4335,20 +4323,14 @@
           <t>QekfJmLa</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B244" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="245">
@@ -4357,20 +4339,14 @@
           <t>8KIT2SzJ</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B245" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="246">
@@ -4379,20 +4355,14 @@
           <t>fcYpyo85</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B246" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="247">
@@ -4401,20 +4371,14 @@
           <t>fqgCMogC</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B247" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3</v>
+      </c>
+      <c r="D247" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="248">
@@ -4423,20 +4387,14 @@
           <t>QwI4i6hn</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B248" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C248" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D248" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="249">
@@ -4445,20 +4403,14 @@
           <t>jPRgZOxI</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B249" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D249" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="250">
@@ -4467,19 +4419,189 @@
           <t>OxQ1X27U</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
+      <c r="B250" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C250" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D250" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>3.50</t>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>tEvOrxAE</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>jBnLKPNO</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>QHtUvT8t</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2.80</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D258"/>
+  <dimension ref="A1:D264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4435,20 +4435,14 @@
           <t>MNr3HRkC</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B251" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3</v>
+      </c>
+      <c r="D251" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="252">
@@ -4457,20 +4451,14 @@
           <t>hA5zaJZp</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B252" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3</v>
+      </c>
+      <c r="D252" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="253">
@@ -4479,20 +4467,14 @@
           <t>IVonL9jm</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
+      <c r="B253" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="C253" t="n">
+        <v>9</v>
+      </c>
+      <c r="D253" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="254">
@@ -4501,20 +4483,14 @@
           <t>OQqSjnv9</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B254" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D254" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="255">
@@ -4523,20 +4499,14 @@
           <t>YcAFQVSP</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B255" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C255" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D255" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="256">
@@ -4545,20 +4515,14 @@
           <t>tEvOrxAE</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B256" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D256" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="257">
@@ -4567,20 +4531,14 @@
           <t>jBnLKPNO</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B257" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D257" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="258">
@@ -4589,19 +4547,145 @@
           <t>QHtUvT8t</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
+      <c r="B258" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>nXUxw7wg</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>Q31eQTgm</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>2.80</t>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>MVf4O7Oa</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>4.00</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D264"/>
+  <dimension ref="A1:D273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,20 +4563,14 @@
           <t>4KmdZaBc</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B259" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="260">
@@ -4585,20 +4579,14 @@
           <t>hpMqQeYq</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B260" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C260" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D260" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="261">
@@ -4607,20 +4595,14 @@
           <t>ChPK4l66</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B261" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C261" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D261" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="262">
@@ -4629,20 +4611,14 @@
           <t>nXUxw7wg</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B262" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D262" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="263">
@@ -4651,20 +4627,14 @@
           <t>Q31eQTgm</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="B263" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3</v>
+      </c>
+      <c r="D263" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="264">
@@ -4673,19 +4643,211 @@
           <t>MVf4O7Oa</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>4.00</t>
+      <c r="B264" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D264" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>x2RBbu6T</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>8MZf2N64</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>4.75</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D273"/>
+  <dimension ref="A1:D277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4659,20 +4659,14 @@
           <t>0ns5XwtA</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
+      <c r="B265" t="n">
+        <v>8</v>
+      </c>
+      <c r="C265" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="266">
@@ -4681,20 +4675,14 @@
           <t>CQ0ABdJj</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B266" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D266" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="267">
@@ -4703,20 +4691,14 @@
           <t>KhwykQ8L</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B267" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C267" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D267" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="268">
@@ -4725,20 +4707,14 @@
           <t>v1KiOZ2d</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B268" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D268" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="269">
@@ -4747,20 +4723,14 @@
           <t>0Y1WIvRG</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B269" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D269" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="270">
@@ -4769,20 +4739,14 @@
           <t>f92vnwe3</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B270" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C270" t="n">
+        <v>3</v>
+      </c>
+      <c r="D270" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="271">
@@ -4791,20 +4755,14 @@
           <t>8CpDVHAM</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
+      <c r="B271" t="n">
+        <v>5</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="272">
@@ -4813,20 +4771,14 @@
           <t>x2RBbu6T</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B272" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D272" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="273">
@@ -4835,19 +4787,101 @@
           <t>8MZf2N64</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>4.75</t>
+      <c r="B273" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C273" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D273" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>2qDTo2MN</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>5.25</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D277"/>
+  <dimension ref="A1:D290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4803,20 +4803,14 @@
           <t>GOO6q4Wr</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B274" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C274" t="n">
+        <v>3</v>
+      </c>
+      <c r="D274" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="275">
@@ -4825,20 +4819,14 @@
           <t>SM0npHPF</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B275" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D275" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="276">
@@ -4847,20 +4835,14 @@
           <t>OlferefS</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B276" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C276" t="n">
+        <v>7</v>
+      </c>
+      <c r="D276" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="277">
@@ -4869,19 +4851,299 @@
           <t>2qDTo2MN</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
+      <c r="B277" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C277" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D277" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
         <is>
           <t>3.25</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>5.25</t>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>lfATGMLc</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>Gnw301yH</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>fJ9LmOiB</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>K0g0ttpo</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>Y3LCkpNb</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>YoStgJTj</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>3.30</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D312"/>
+  <dimension ref="A1:D324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5283,20 +5283,14 @@
           <t>8EcB5Oig</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B304" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C304" t="n">
+        <v>3</v>
+      </c>
+      <c r="D304" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="305">
@@ -5305,20 +5299,14 @@
           <t>CjIFsr1e</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B305" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C305" t="n">
+        <v>3</v>
+      </c>
+      <c r="D305" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="306">
@@ -5327,20 +5315,14 @@
           <t>08zpk37C</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B306" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D306" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="307">
@@ -5349,20 +5331,14 @@
           <t>YeqTho8m</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B307" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C307" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D307" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="308">
@@ -5371,20 +5347,14 @@
           <t>YR7dTBSH</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B308" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C308" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D308" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="309">
@@ -5393,20 +5363,14 @@
           <t>KOsNECDO</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B309" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C309" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D309" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="310">
@@ -5415,20 +5379,14 @@
           <t>jqj6IfEa</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B310" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C310" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D310" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="311">
@@ -5437,20 +5395,14 @@
           <t>Q14lVXc5</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B311" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C311" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D311" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="312">
@@ -5459,19 +5411,277 @@
           <t>4SibKGqm</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
+      <c r="B312" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C312" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D312" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
         <is>
           <t>3.20</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>dMUW3ea6</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>nBqFGYrC</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>hlOu2ZTI</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>KfGRPxMP</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>4nGuXgTh</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>bkDXYFbt</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2.80</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D312"/>
+  <dimension ref="A1:D346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5283,20 +5283,14 @@
           <t>8EcB5Oig</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B304" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C304" t="n">
+        <v>3</v>
+      </c>
+      <c r="D304" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="305">
@@ -5305,20 +5299,14 @@
           <t>CjIFsr1e</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B305" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C305" t="n">
+        <v>3</v>
+      </c>
+      <c r="D305" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="306">
@@ -5327,20 +5315,14 @@
           <t>08zpk37C</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B306" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D306" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="307">
@@ -5349,20 +5331,14 @@
           <t>YeqTho8m</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B307" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C307" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D307" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="308">
@@ -5371,20 +5347,14 @@
           <t>YR7dTBSH</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B308" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C308" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D308" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="309">
@@ -5393,20 +5363,14 @@
           <t>KOsNECDO</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B309" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C309" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D309" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="310">
@@ -5415,20 +5379,14 @@
           <t>jqj6IfEa</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B310" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C310" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D310" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="311">
@@ -5437,20 +5395,14 @@
           <t>Q14lVXc5</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B311" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C311" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D311" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="312">
@@ -5459,19 +5411,761 @@
           <t>4SibKGqm</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
+      <c r="B312" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C312" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D312" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
         <is>
           <t>3.20</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>SSPUA3Cj</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>QZsHWpZ9</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>KMCGY64c</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>Cj6bqOIF</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>0GvnzKu2</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>v1jwxtBk</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>vw8jopl3</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>YaoPUO3M</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>QcQ3Ntdd</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>IXMeP2Rq</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>dMUW3ea6</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>nBqFGYrC</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>hlOu2ZTI</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>KfGRPxMP</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>4nGuXgTh</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>bkDXYFbt</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2.80</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5427,20 +5427,14 @@
           <t>QiF6bS1N</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B313" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C313" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="314">
@@ -5449,20 +5443,14 @@
           <t>pxdwg6Pp</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="B314" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C314" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="315">
@@ -5471,20 +5459,14 @@
           <t>OAmz0KLU</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B315" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C315" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D315" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="316">
@@ -5493,20 +5475,14 @@
           <t>dCNk2A2b</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B316" t="n">
+        <v>2</v>
+      </c>
+      <c r="C316" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D316" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="317">
@@ -5515,20 +5491,14 @@
           <t>ImLNuMV7</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
+      <c r="B317" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="C317" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D317" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="318">
@@ -5537,20 +5507,14 @@
           <t>xWrPG9Hi</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B318" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C318" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D318" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -5559,20 +5523,14 @@
           <t>4b2YCRGG</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B319" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D319" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="320">
@@ -5581,20 +5539,14 @@
           <t>dYbQEmn4</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B320" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C320" t="n">
+        <v>3</v>
+      </c>
+      <c r="D320" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="321">
@@ -5603,20 +5555,14 @@
           <t>IRBb0lXA</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B321" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C321" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D321" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="322">
@@ -5625,20 +5571,14 @@
           <t>xjut9IFr</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B322" t="n">
+        <v>4</v>
+      </c>
+      <c r="C322" t="n">
+        <v>3</v>
+      </c>
+      <c r="D322" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="323">
@@ -5647,20 +5587,14 @@
           <t>8b5vHIeT</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B323" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C323" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D323" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="324">
@@ -5669,20 +5603,14 @@
           <t>AyPaTn1c</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B324" t="n">
+        <v>3</v>
+      </c>
+      <c r="C324" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D324" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -5691,20 +5619,14 @@
           <t>fVeJ32M5</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B325" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C325" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D325" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="326">
@@ -5713,20 +5635,14 @@
           <t>SdHeBgOE</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B326" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C326" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D326" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="327">
@@ -5735,20 +5651,14 @@
           <t>dzUhmsxP</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B327" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C327" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D327" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="328">
@@ -5757,20 +5667,14 @@
           <t>na927pNt</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B328" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C328" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D328" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="329">
@@ -5779,20 +5683,14 @@
           <t>SfxxiPx0</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B329" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C329" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D329" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="330">
@@ -5801,20 +5699,14 @@
           <t>jckS1tiI</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B330" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C330" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="331">
@@ -5823,20 +5715,14 @@
           <t>SSPUA3Cj</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B331" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C331" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D331" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="332">
@@ -5845,20 +5731,14 @@
           <t>QZsHWpZ9</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B332" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C332" t="n">
+        <v>3</v>
+      </c>
+      <c r="D332" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="333">
@@ -5867,20 +5747,14 @@
           <t>KMCGY64c</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B333" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C333" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D333" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="334">
@@ -5889,20 +5763,14 @@
           <t>Cj6bqOIF</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B334" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C334" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="335">
@@ -5911,20 +5779,14 @@
           <t>0GvnzKu2</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B335" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C335" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D335" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="336">
@@ -5933,20 +5795,14 @@
           <t>v1jwxtBk</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B336" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C336" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D336" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="337">
@@ -5955,20 +5811,14 @@
           <t>vw8jopl3</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B337" t="n">
+        <v>2</v>
+      </c>
+      <c r="C337" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D337" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="338">
@@ -5977,20 +5827,14 @@
           <t>YaoPUO3M</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B338" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C338" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D338" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="339">
@@ -5999,20 +5843,14 @@
           <t>QcQ3Ntdd</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B339" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C339" t="n">
+        <v>3</v>
+      </c>
+      <c r="D339" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="340">
@@ -6021,20 +5859,14 @@
           <t>IXMeP2Rq</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B340" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C340" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D340" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="341">
@@ -6043,20 +5875,14 @@
           <t>dMUW3ea6</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B341" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C341" t="n">
+        <v>4</v>
+      </c>
+      <c r="D341" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="342">
@@ -6065,20 +5891,14 @@
           <t>nBqFGYrC</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B342" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C342" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D342" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="343">
@@ -6087,20 +5907,14 @@
           <t>hlOu2ZTI</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B343" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C343" t="n">
+        <v>3</v>
+      </c>
+      <c r="D343" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="344">
@@ -6109,20 +5923,14 @@
           <t>KfGRPxMP</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B344" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C344" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D344" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="345">
@@ -6131,20 +5939,14 @@
           <t>4nGuXgTh</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B345" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C345" t="n">
+        <v>4</v>
+      </c>
+      <c r="D345" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="346">
@@ -6153,19 +5955,57 @@
           <t>bkDXYFbt</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>2.80</t>
+      <c r="B346" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C346" t="n">
+        <v>3</v>
+      </c>
+      <c r="D346" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>8Ia7s2mS</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>3.30</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5427,20 +5427,14 @@
           <t>QiF6bS1N</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B313" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C313" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="314">
@@ -5449,20 +5443,14 @@
           <t>pxdwg6Pp</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="B314" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C314" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="315">
@@ -5471,20 +5459,14 @@
           <t>OAmz0KLU</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B315" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C315" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D315" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="316">
@@ -5493,20 +5475,14 @@
           <t>dCNk2A2b</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B316" t="n">
+        <v>2</v>
+      </c>
+      <c r="C316" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D316" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="317">
@@ -5515,20 +5491,14 @@
           <t>ImLNuMV7</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
+      <c r="B317" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="C317" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D317" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="318">
@@ -5537,20 +5507,14 @@
           <t>xWrPG9Hi</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B318" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C318" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D318" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -5559,20 +5523,14 @@
           <t>4b2YCRGG</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B319" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D319" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="320">
@@ -5581,20 +5539,14 @@
           <t>dYbQEmn4</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B320" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C320" t="n">
+        <v>3</v>
+      </c>
+      <c r="D320" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="321">
@@ -5603,20 +5555,14 @@
           <t>IRBb0lXA</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B321" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C321" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D321" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="322">
@@ -5625,20 +5571,14 @@
           <t>xjut9IFr</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B322" t="n">
+        <v>4</v>
+      </c>
+      <c r="C322" t="n">
+        <v>3</v>
+      </c>
+      <c r="D322" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="323">
@@ -5647,20 +5587,14 @@
           <t>8b5vHIeT</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B323" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C323" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D323" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="324">
@@ -5669,20 +5603,14 @@
           <t>AyPaTn1c</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B324" t="n">
+        <v>3</v>
+      </c>
+      <c r="C324" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D324" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -5691,20 +5619,14 @@
           <t>fVeJ32M5</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B325" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C325" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D325" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="326">
@@ -5713,20 +5635,14 @@
           <t>SdHeBgOE</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B326" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C326" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D326" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="327">
@@ -5735,20 +5651,14 @@
           <t>dzUhmsxP</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B327" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C327" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D327" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="328">
@@ -5757,20 +5667,14 @@
           <t>na927pNt</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B328" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C328" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D328" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="329">
@@ -5779,20 +5683,14 @@
           <t>SfxxiPx0</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B329" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C329" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D329" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="330">
@@ -5801,20 +5699,14 @@
           <t>jckS1tiI</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B330" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C330" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="331">
@@ -5823,20 +5715,14 @@
           <t>SSPUA3Cj</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B331" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C331" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D331" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="332">
@@ -5845,20 +5731,14 @@
           <t>QZsHWpZ9</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B332" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C332" t="n">
+        <v>3</v>
+      </c>
+      <c r="D332" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="333">
@@ -5867,20 +5747,14 @@
           <t>KMCGY64c</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B333" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C333" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D333" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="334">
@@ -5889,20 +5763,14 @@
           <t>Cj6bqOIF</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B334" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C334" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="335">
@@ -5911,20 +5779,14 @@
           <t>0GvnzKu2</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B335" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C335" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D335" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="336">
@@ -5933,20 +5795,14 @@
           <t>v1jwxtBk</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B336" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C336" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D336" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="337">
@@ -5955,20 +5811,14 @@
           <t>vw8jopl3</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B337" t="n">
+        <v>2</v>
+      </c>
+      <c r="C337" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D337" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="338">
@@ -5977,20 +5827,14 @@
           <t>YaoPUO3M</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B338" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C338" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D338" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="339">
@@ -5999,20 +5843,14 @@
           <t>QcQ3Ntdd</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B339" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C339" t="n">
+        <v>3</v>
+      </c>
+      <c r="D339" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="340">
@@ -6021,20 +5859,14 @@
           <t>IXMeP2Rq</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B340" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C340" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D340" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="341">
@@ -6043,20 +5875,14 @@
           <t>dMUW3ea6</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B341" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C341" t="n">
+        <v>4</v>
+      </c>
+      <c r="D341" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="342">
@@ -6065,20 +5891,14 @@
           <t>nBqFGYrC</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B342" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C342" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D342" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="343">
@@ -6087,20 +5907,14 @@
           <t>hlOu2ZTI</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B343" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C343" t="n">
+        <v>3</v>
+      </c>
+      <c r="D343" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="344">
@@ -6109,20 +5923,14 @@
           <t>KfGRPxMP</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B344" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C344" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D344" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="345">
@@ -6131,20 +5939,14 @@
           <t>4nGuXgTh</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B345" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C345" t="n">
+        <v>4</v>
+      </c>
+      <c r="D345" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="346">
@@ -6153,19 +5955,233 @@
           <t>bkDXYFbt</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>2.80</t>
+      <c r="B346" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C346" t="n">
+        <v>3</v>
+      </c>
+      <c r="D346" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>8Ia7s2mS</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>3.30</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D356"/>
+  <dimension ref="A1:D366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5971,20 +5971,14 @@
           <t>pGrl7dpe</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B347" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C347" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D347" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="348">
@@ -5993,20 +5987,14 @@
           <t>bqbA3PNE</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B348" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C348" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D348" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="349">
@@ -6015,20 +6003,14 @@
           <t>6VWd5zF7</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B349" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C349" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D349" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="350">
@@ -6037,20 +6019,14 @@
           <t>QDjsB5oT</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
+      <c r="B350" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C350" t="n">
+        <v>7</v>
+      </c>
+      <c r="D350" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="351">
@@ -6059,20 +6035,14 @@
           <t>ddsD5q9j</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B351" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C351" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D351" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="352">
@@ -6081,20 +6051,14 @@
           <t>f5SjRHyR</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
+      <c r="B352" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C352" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D352" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="353">
@@ -6103,20 +6067,14 @@
           <t>rkN7RQV9</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B353" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C353" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D353" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="354">
@@ -6125,20 +6083,14 @@
           <t>bwZsTw7E</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B354" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C354" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D354" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="355">
@@ -6147,20 +6099,14 @@
           <t>445r4WXo</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B355" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C355" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D355" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="356">
@@ -6169,17 +6115,231 @@
           <t>8Ia7s2mS</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
+      <c r="B356" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C356" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D356" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
         <is>
           <t>2.90</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>n7g3az9D</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>SteFA0HE</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>bB6CjuQr</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>CnAE6iGt</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>6DRXcNX8</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D366"/>
+  <dimension ref="A1:D375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6131,20 +6131,14 @@
           <t>4vvdzeEs</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="B357" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C357" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D357" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="358">
@@ -6153,20 +6147,14 @@
           <t>YemQuHjK</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B358" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C358" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D358" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="359">
@@ -6175,20 +6163,14 @@
           <t>KSw0hfzQ</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B359" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C359" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D359" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="360">
@@ -6197,20 +6179,14 @@
           <t>hMoEUjrJ</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B360" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C360" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D360" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="361">
@@ -6219,20 +6195,14 @@
           <t>06X4YYrf</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B361" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C361" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D361" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="362">
@@ -6241,20 +6211,14 @@
           <t>n7g3az9D</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B362" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C362" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D362" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="363">
@@ -6263,20 +6227,14 @@
           <t>SteFA0HE</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B363" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C363" t="n">
+        <v>3</v>
+      </c>
+      <c r="D363" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="364">
@@ -6285,20 +6243,14 @@
           <t>bB6CjuQr</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B364" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C364" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D364" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="365">
@@ -6307,20 +6259,14 @@
           <t>CnAE6iGt</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B365" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C365" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D365" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="366">
@@ -6329,19 +6275,211 @@
           <t>6DRXcNX8</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B366" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C366" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D366" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>noISncP7</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>S4w21dv1</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2uLtd12L</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>fw0LlJfe</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>z7bN8vnR</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>3.30</t>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>3.10</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D398"/>
+  <dimension ref="A1:D418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6643,20 +6643,14 @@
           <t>CvbDaBsg</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B389" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C389" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D389" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="390">
@@ -6665,20 +6659,14 @@
           <t>YgnMckC5</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B390" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C390" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D390" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="391">
@@ -6687,20 +6675,14 @@
           <t>hzRnqjcC</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
+      <c r="B391" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C391" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D391" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="392">
@@ -6709,20 +6691,14 @@
           <t>4Ef51XCt</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B392" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C392" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D392" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="393">
@@ -6731,20 +6707,14 @@
           <t>CQIvoCSa</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B393" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C393" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D393" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="394">
@@ -6753,20 +6723,14 @@
           <t>Y1bN4Vpg</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B394" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C394" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D394" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="395">
@@ -6775,20 +6739,14 @@
           <t>n5OdJUan</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B395" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C395" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D395" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="396">
@@ -6797,20 +6755,14 @@
           <t>lCTKDQTN</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B396" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C396" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D396" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="397">
@@ -6819,20 +6771,14 @@
           <t>zRfv1mpI</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B397" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C397" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D397" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="398">
@@ -6841,19 +6787,441 @@
           <t>GpGDFnaB</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
+      <c r="B398" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C398" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D398" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>4Id1wB8F</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2FgfSPrH</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>O8lguXw3</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>zm8bJkHq</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>z5JYK2hl</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr">
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>44HSOBgM</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>OUs3Q3DT</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>Cl3JSgfc</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>fDYYKsyi</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>p21RQXO9</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>Wbg14s0S</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>nBJcpM8d</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2J1p8P03</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>8dtBgQoA</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>nPbWbLNk</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>zXah63VF</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
         <is>
           <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>CUn2enHc</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>0fLknrvp</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>GMqJi4GM</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>8vmucah2</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>3.20</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D418"/>
+  <dimension ref="A1:D428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6803,20 +6803,14 @@
           <t>4Id1wB8F</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B399" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C399" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D399" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="400">
@@ -6825,20 +6819,14 @@
           <t>2FgfSPrH</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B400" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C400" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D400" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="401">
@@ -6847,20 +6835,14 @@
           <t>O8lguXw3</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B401" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C401" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D401" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="402">
@@ -6869,20 +6851,14 @@
           <t>zm8bJkHq</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B402" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C402" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D402" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="403">
@@ -6891,20 +6867,14 @@
           <t>z5JYK2hl</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B403" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C403" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D403" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="404">
@@ -6913,20 +6883,14 @@
           <t>44HSOBgM</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B404" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C404" t="n">
+        <v>3</v>
+      </c>
+      <c r="D404" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="405">
@@ -6935,20 +6899,14 @@
           <t>OUs3Q3DT</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B405" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C405" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D405" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="406">
@@ -6957,20 +6915,14 @@
           <t>Cl3JSgfc</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B406" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C406" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D406" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="407">
@@ -6979,20 +6931,14 @@
           <t>fDYYKsyi</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B407" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C407" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D407" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="408">
@@ -7001,20 +6947,14 @@
           <t>p21RQXO9</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B408" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C408" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D408" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="409">
@@ -7023,20 +6963,14 @@
           <t>Wbg14s0S</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B409" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C409" t="n">
+        <v>8</v>
+      </c>
+      <c r="D409" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="410">
@@ -7045,20 +6979,14 @@
           <t>nBJcpM8d</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B410" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C410" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D410" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="411">
@@ -7067,20 +6995,14 @@
           <t>2J1p8P03</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B411" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C411" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D411" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="412">
@@ -7099,20 +7021,14 @@
           <t>nPbWbLNk</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
+      <c r="B413" t="n">
+        <v>5</v>
+      </c>
+      <c r="C413" t="n">
+        <v>4</v>
+      </c>
+      <c r="D413" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="414">
@@ -7121,20 +7037,14 @@
           <t>zXah63VF</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B414" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C414" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D414" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="415">
@@ -7143,20 +7053,14 @@
           <t>CUn2enHc</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="B415" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C415" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D415" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="416">
@@ -7165,20 +7069,14 @@
           <t>0fLknrvp</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B416" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C416" t="n">
+        <v>7</v>
+      </c>
+      <c r="D416" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="417">
@@ -7187,20 +7085,14 @@
           <t>GMqJi4GM</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B417" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C417" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D417" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="418">
@@ -7209,19 +7101,233 @@
           <t>8vmucah2</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
+      <c r="B418" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C418" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D418" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>h2NyhKup</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>KhgxuOqK</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>fZPXTcyJ</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>3.20</t>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>URv8Z17s</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>KCHJi1TP</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>CAdbpJLa</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>d2d7HTod</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>3.10</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D428"/>
+  <dimension ref="A1:D440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7117,20 +7117,14 @@
           <t>h2NyhKup</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B419" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C419" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D419" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="420">
@@ -7139,20 +7133,14 @@
           <t>ll7vCuXF</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B420" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C420" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D420" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="421">
@@ -7161,20 +7149,14 @@
           <t>YNHbsZ6C</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
+      <c r="B421" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C421" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D421" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="422">
@@ -7183,20 +7165,14 @@
           <t>Gz9WD123</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B422" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C422" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D422" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="423">
@@ -7205,20 +7181,14 @@
           <t>KhgxuOqK</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B423" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C423" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D423" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="424">
@@ -7227,20 +7197,14 @@
           <t>fZPXTcyJ</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B424" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C424" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D424" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="425">
@@ -7249,20 +7213,14 @@
           <t>URv8Z17s</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B425" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C425" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D425" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="426">
@@ -7271,20 +7229,14 @@
           <t>KCHJi1TP</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B426" t="n">
+        <v>3</v>
+      </c>
+      <c r="C426" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D426" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="427">
@@ -7293,20 +7245,14 @@
           <t>CAdbpJLa</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B427" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C427" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D427" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="428">
@@ -7315,19 +7261,217 @@
           <t>d2d7HTod</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>3.10</t>
+      <c r="B428" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C428" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D428" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2Xrca2mA</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C429" t="n">
+        <v>6</v>
+      </c>
+      <c r="D429" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>f1xuAJ1S</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C430" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D430" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>65kl1OIc</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C431" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D431" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>0SQqjbAd</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C432" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D432" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>8Uo5ctIM</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C433" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D433" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>QgYGXuxf</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C434" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D434" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>4pgjnuim</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>2</v>
+      </c>
+      <c r="C435" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D435" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>b7WOVJ66</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C436" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D436" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>vcGkHKiD</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C437" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D437" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>8xj7rcjC</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C438" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D438" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>QqTA4cPk</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>WWCsJtN0</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>3.60</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D440"/>
+  <dimension ref="A1:D448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7437,20 +7437,14 @@
           <t>QqTA4cPk</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B439" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C439" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D439" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="440">
@@ -7459,19 +7453,189 @@
           <t>WWCsJtN0</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B440" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C440" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D440" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>67jtezzI</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>CpD7BeKb</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>U1eH0v6t</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
         <is>
           <t>3.60</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>GIJbDHkn</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>06qkgE4U</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>bsmYdd55</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>xSbPbIzg</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>QFRek53d</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>6.00</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D448"/>
+  <dimension ref="A1:D472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7469,20 +7469,14 @@
           <t>67jtezzI</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B441" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C441" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D441" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="442">
@@ -7491,20 +7485,14 @@
           <t>CpD7BeKb</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B442" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C442" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D442" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="443">
@@ -7513,20 +7501,14 @@
           <t>U1eH0v6t</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B443" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C443" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D443" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="444">
@@ -7535,20 +7517,14 @@
           <t>GIJbDHkn</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B444" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C444" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D444" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="445">
@@ -7557,20 +7533,14 @@
           <t>06qkgE4U</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B445" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C445" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D445" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="446">
@@ -7579,20 +7549,14 @@
           <t>bsmYdd55</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B446" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C446" t="n">
+        <v>3</v>
+      </c>
+      <c r="D446" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="447">
@@ -7601,20 +7565,14 @@
           <t>xSbPbIzg</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B447" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C447" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D447" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -7623,19 +7581,409 @@
           <t>QFRek53d</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
+      <c r="B448" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C448" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D448" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>2</v>
+      </c>
+      <c r="C449" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D449" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C450" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D450" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>dhkQFrkl</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>2</v>
+      </c>
+      <c r="C451" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D451" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>x88gL4RQ</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C452" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D452" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>vymauDyP</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C453" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D453" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>A31a9QfS</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C454" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D454" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>YFoDELW7</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C455" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D455" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>Ey8jBnQF</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C456" t="n">
+        <v>3</v>
+      </c>
+      <c r="D456" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>Qkr5Gs2e</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C457" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D457" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>tjlFtyLO</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C458" t="n">
+        <v>3</v>
+      </c>
+      <c r="D458" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>KAGF9ZlB</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C459" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D459" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>vaTmiRYq</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C460" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D460" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C461" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D461" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C462" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D462" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C463" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D463" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C464" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D464" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>EkmPPou9</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C465" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D465" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>tO9rD8e3</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C466" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D466" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>AHtYNP9L</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C467" t="n">
+        <v>3</v>
+      </c>
+      <c r="D467" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>QT6U34Ik</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C468" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D468" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>6mS3I3Xr</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C469" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D469" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>EBOaxPOE</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C470" t="n">
+        <v>3</v>
+      </c>
+      <c r="D470" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>nqew2rm2</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
         <is>
           <t>3.30</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>6.00</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D472"/>
+  <dimension ref="A1:D520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7949,20 +7949,14 @@
           <t>E595Qvn9</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B471" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C471" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D471" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="472">
@@ -7971,19 +7965,1065 @@
           <t>nqew2rm2</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
+      <c r="B472" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C472" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D472" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>G0EJ1qlU</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>K8uZCRtP</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>QZBZmK7d</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>GraCJHdl</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>51.00</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>41.00</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>fR1YQYGr</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>4rI4FQ1U</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>41.00</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>OSUPZTaD</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>S0NREmCC</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>jZMBcXiK</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>tOyaCZ1k</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>8z7vNj3t</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>51.00</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>dbIuPwZQ</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>51.00</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>8WGS5hTs</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>Kh3g99kt</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>GzRen7Wi</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>bLVAIVCm</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>xGbeJ825</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>41.00</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>QBB2WfgL</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
         <is>
           <t>3.30</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>dbbI35JH</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>GtjsPCoe</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>4bAy4Wcf</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>U7IQktwp</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>fmw9wC0l</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>vFyxof8E</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>SEGkjkpf</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>vykvOikQ</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2DtHyjV0</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>C0VdBE5K</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>CSZqqYxR</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>SI617mKh</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>UqIgYGO8</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>bPRfe2FM</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>pvyUHevS</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>CODq2AS6</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>W6D6n7qJ</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>xAwncOpA</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>KY6Lt30T</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>34.00</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>WYTIG9s0</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>O6gkNjG7</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>Yw2h0lcJ</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>Mu2KHeR0</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>41.00</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>OtUL91UF</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>UudgigEl</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>ITbLBNa3</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>xjF4po14</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>51.00</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>f1IshBFs</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>8drFZTnn</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>67.00</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>O6DCrPVG</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>1.45</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D520"/>
+  <dimension ref="A1:D535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7981,20 +7981,14 @@
           <t>G0EJ1qlU</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="B473" t="n">
+        <v>9</v>
+      </c>
+      <c r="C473" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D473" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="474">
@@ -8003,20 +7997,14 @@
           <t>K8uZCRtP</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="B474" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C474" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D474" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="475">
@@ -8025,20 +8013,14 @@
           <t>QZBZmK7d</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="B475" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C475" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D475" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="476">
@@ -8047,15 +8029,11 @@
           <t>GraCJHdl</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>51.00</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>41.00</t>
-        </is>
+      <c r="B476" t="n">
+        <v>51</v>
+      </c>
+      <c r="C476" t="n">
+        <v>41</v>
       </c>
       <c r="D476" t="inlineStr"/>
     </row>
@@ -8065,20 +8043,14 @@
           <t>fR1YQYGr</t>
         </is>
       </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="B477" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C477" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D477" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="478">
@@ -8087,20 +8059,14 @@
           <t>4rI4FQ1U</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>41.00</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
+      <c r="B478" t="n">
+        <v>41</v>
+      </c>
+      <c r="C478" t="n">
+        <v>17</v>
+      </c>
+      <c r="D478" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="479">
@@ -8109,20 +8075,14 @@
           <t>OSUPZTaD</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B479" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C479" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D479" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -8131,20 +8091,14 @@
           <t>S0NREmCC</t>
         </is>
       </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
+      <c r="B480" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="C480" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D480" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="481">
@@ -8153,20 +8107,14 @@
           <t>jZMBcXiK</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B481" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C481" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D481" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="482">
@@ -8175,20 +8123,14 @@
           <t>tOyaCZ1k</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B482" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C482" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D482" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="483">
@@ -8197,20 +8139,14 @@
           <t>8z7vNj3t</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>51.00</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
+      <c r="B483" t="n">
+        <v>51</v>
+      </c>
+      <c r="C483" t="n">
+        <v>26</v>
+      </c>
+      <c r="D483" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="484">
@@ -8219,20 +8155,14 @@
           <t>dbIuPwZQ</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>51.00</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>23.00</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
+      <c r="B484" t="n">
+        <v>51</v>
+      </c>
+      <c r="C484" t="n">
+        <v>23</v>
+      </c>
+      <c r="D484" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="485">
@@ -8241,20 +8171,14 @@
           <t>8WGS5hTs</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B485" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C485" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D485" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="486">
@@ -8263,20 +8187,14 @@
           <t>Kh3g99kt</t>
         </is>
       </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B486" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C486" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D486" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="487">
@@ -8285,20 +8203,14 @@
           <t>GzRen7Wi</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
+      <c r="B487" t="n">
+        <v>26</v>
+      </c>
+      <c r="C487" t="n">
+        <v>11</v>
+      </c>
+      <c r="D487" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="488">
@@ -8307,20 +8219,14 @@
           <t>bLVAIVCm</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="B488" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C488" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D488" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="489">
@@ -8329,20 +8235,14 @@
           <t>xGbeJ825</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>41.00</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
+      <c r="B489" t="n">
+        <v>41</v>
+      </c>
+      <c r="C489" t="n">
+        <v>21</v>
+      </c>
+      <c r="D489" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="490">
@@ -8351,20 +8251,14 @@
           <t>QBB2WfgL</t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B490" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C490" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D490" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="491">
@@ -8373,20 +8267,14 @@
           <t>dbbI35JH</t>
         </is>
       </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="B491" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C491" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D491" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="492">
@@ -8395,20 +8283,14 @@
           <t>GtjsPCoe</t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="B492" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C492" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D492" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="493">
@@ -8417,20 +8299,14 @@
           <t>4bAy4Wcf</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="B493" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C493" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D493" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="494">
@@ -8439,20 +8315,14 @@
           <t>U7IQktwp</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
+      <c r="B494" t="n">
+        <v>19</v>
+      </c>
+      <c r="C494" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D494" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="495">
@@ -8461,20 +8331,14 @@
           <t>fmw9wC0l</t>
         </is>
       </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="B495" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C495" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D495" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="496">
@@ -8483,20 +8347,14 @@
           <t>vFyxof8E</t>
         </is>
       </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B496" t="n">
+        <v>4</v>
+      </c>
+      <c r="C496" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D496" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="497">
@@ -8505,20 +8363,14 @@
           <t>SEGkjkpf</t>
         </is>
       </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B497" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C497" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D497" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="498">
@@ -8527,20 +8379,14 @@
           <t>vykvOikQ</t>
         </is>
       </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B498" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C498" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D498" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="499">
@@ -8549,20 +8395,14 @@
           <t>2DtHyjV0</t>
         </is>
       </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B499" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C499" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D499" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="500">
@@ -8571,20 +8411,14 @@
           <t>C0VdBE5K</t>
         </is>
       </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B500" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C500" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D500" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="501">
@@ -8593,20 +8427,14 @@
           <t>CSZqqYxR</t>
         </is>
       </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B501" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C501" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D501" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="502">
@@ -8615,20 +8443,14 @@
           <t>SI617mKh</t>
         </is>
       </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="B502" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C502" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D502" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="503">
@@ -8637,20 +8459,14 @@
           <t>UqIgYGO8</t>
         </is>
       </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B503" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C503" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D503" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="504">
@@ -8659,20 +8475,14 @@
           <t>bPRfe2FM</t>
         </is>
       </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="B504" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C504" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D504" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="505">
@@ -8681,20 +8491,14 @@
           <t>pvyUHevS</t>
         </is>
       </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B505" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C505" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D505" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="506">
@@ -8703,20 +8507,14 @@
           <t>CODq2AS6</t>
         </is>
       </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="B506" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C506" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D506" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="507">
@@ -8725,20 +8523,14 @@
           <t>W6D6n7qJ</t>
         </is>
       </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B507" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C507" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D507" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="508">
@@ -8747,20 +8539,14 @@
           <t>xAwncOpA</t>
         </is>
       </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
+      <c r="B508" t="n">
+        <v>11</v>
+      </c>
+      <c r="C508" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D508" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="509">
@@ -8769,20 +8555,14 @@
           <t>KY6Lt30T</t>
         </is>
       </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>34.00</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
+      <c r="B509" t="n">
+        <v>34</v>
+      </c>
+      <c r="C509" t="n">
+        <v>13</v>
+      </c>
+      <c r="D509" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="510">
@@ -8791,20 +8571,14 @@
           <t>WYTIG9s0</t>
         </is>
       </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B510" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C510" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D510" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="511">
@@ -8813,20 +8587,14 @@
           <t>O6gkNjG7</t>
         </is>
       </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="B511" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C511" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D511" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="512">
@@ -8835,20 +8603,14 @@
           <t>Yw2h0lcJ</t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B512" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C512" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D512" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="513">
@@ -8857,20 +8619,14 @@
           <t>Mu2KHeR0</t>
         </is>
       </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>41.00</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
+      <c r="B513" t="n">
+        <v>41</v>
+      </c>
+      <c r="C513" t="n">
+        <v>17</v>
+      </c>
+      <c r="D513" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="514">
@@ -8879,20 +8635,14 @@
           <t>OtUL91UF</t>
         </is>
       </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="B514" t="n">
+        <v>7</v>
+      </c>
+      <c r="C514" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D514" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="515">
@@ -8901,20 +8651,14 @@
           <t>UudgigEl</t>
         </is>
       </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
+      <c r="B515" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C515" t="n">
+        <v>4</v>
+      </c>
+      <c r="D515" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="516">
@@ -8923,20 +8667,14 @@
           <t>ITbLBNa3</t>
         </is>
       </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="B516" t="n">
+        <v>6</v>
+      </c>
+      <c r="C516" t="n">
+        <v>4</v>
+      </c>
+      <c r="D516" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="517">
@@ -8945,20 +8683,14 @@
           <t>xjF4po14</t>
         </is>
       </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>51.00</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
+      <c r="B517" t="n">
+        <v>51</v>
+      </c>
+      <c r="C517" t="n">
+        <v>17</v>
+      </c>
+      <c r="D517" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="518">
@@ -8967,20 +8699,14 @@
           <t>f1IshBFs</t>
         </is>
       </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B518" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C518" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D518" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="519">
@@ -8989,20 +8715,14 @@
           <t>8drFZTnn</t>
         </is>
       </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>67.00</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
+      <c r="B519" t="n">
+        <v>67</v>
+      </c>
+      <c r="C519" t="n">
+        <v>26</v>
+      </c>
+      <c r="D519" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="520">
@@ -9011,19 +8731,259 @@
           <t>O6DCrPVG</t>
         </is>
       </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
+      <c r="B520" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C520" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D520" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C521" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D521" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C522" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D522" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C523" t="n">
+        <v>8</v>
+      </c>
+      <c r="D523" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C524" t="n">
+        <v>5</v>
+      </c>
+      <c r="D524" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C525" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D525" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C526" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D526" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C527" t="n">
+        <v>3</v>
+      </c>
+      <c r="D527" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>rRUgTu3b</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C528" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D528" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>l6zUubV6</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C529" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D529" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>hvsLsK0f</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C530" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D530" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>xURoV1Yo</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C531" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D531" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>vg8vVtHl</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C532" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D532" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>MJYyvx0J</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C533" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D533" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>8YaeRbGD</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C534" t="n">
+        <v>3</v>
+      </c>
+      <c r="D534" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
         <is>
           <t>4.20</t>
-        </is>
-      </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>1.45</t>
         </is>
       </c>
     </row>
